--- a/public/quran-checksum.xlsx
+++ b/public/quran-checksum.xlsx
@@ -29,7 +29,7 @@
     <t>E: Odd (A+B)</t>
   </si>
   <si>
-    <t>F: Chapter if Even</t>
+    <t>F: Surah if Even</t>
   </si>
   <si>
     <t>G: Verses if Odd</t>
